--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125110495</v>
+        <v>125110297</v>
       </c>
       <c r="B2" t="n">
-        <v>57519</v>
+        <v>91032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579536</v>
+        <v>579324</v>
       </c>
       <c r="R2" t="n">
-        <v>6417623</v>
+        <v>6417713</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,17 +764,13 @@
           <t>2025-05-15</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Nu bebott av nötväcka!</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125110121</v>
+        <v>125110495</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>57519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,33 +805,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579349</v>
+        <v>579536</v>
       </c>
       <c r="R3" t="n">
-        <v>6417761</v>
+        <v>6417623</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,6 +873,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Nu bebott av nötväcka!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125110359</v>
+        <v>125110184</v>
       </c>
       <c r="B4" t="n">
-        <v>57918</v>
+        <v>57761</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,33 +916,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -952,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579299</v>
+        <v>579324</v>
       </c>
       <c r="R4" t="n">
-        <v>6417671</v>
+        <v>6417713</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1014,7 +1018,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125110142</v>
+        <v>125110359</v>
       </c>
       <c r="B5" t="n">
         <v>57918</v>
@@ -1058,14 +1062,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 23021, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579356</v>
+        <v>579299</v>
       </c>
       <c r="R5" t="n">
-        <v>6417758</v>
+        <v>6417671</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1124,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110571</v>
+        <v>125110523</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>91032</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1162,13 +1166,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1220,6 +1223,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110297</v>
+        <v>125110142</v>
       </c>
       <c r="B7" t="n">
-        <v>91032</v>
+        <v>57918</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,52 +1254,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>103037</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23021, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579324</v>
+        <v>579356</v>
       </c>
       <c r="R7" t="n">
-        <v>6417713</v>
+        <v>6417758</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,7 +1334,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125110444</v>
+        <v>125110121</v>
       </c>
       <c r="B8" t="n">
-        <v>90063</v>
+        <v>57761</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>889</v>
+        <v>103012</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Irpicodon pendulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1390,12 +1390,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1403,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579436</v>
+        <v>579349</v>
       </c>
       <c r="R8" t="n">
-        <v>6417634</v>
+        <v>6417761</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,18 +1442,12 @@
           <t>2025-05-15</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Mkt gammal tall på berget.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1581,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110180</v>
+        <v>125110326</v>
       </c>
       <c r="B10" t="n">
-        <v>56821</v>
+        <v>91032</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,39 +1588,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100038</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1633,13 +1627,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579324</v>
+        <v>579314</v>
       </c>
       <c r="R10" t="n">
-        <v>6417713</v>
+        <v>6417689</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1677,6 +1671,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1695,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110326</v>
+        <v>125110444</v>
       </c>
       <c r="B11" t="n">
-        <v>91032</v>
+        <v>90063</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,31 +1706,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>889</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Irpicodon pendulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1746,13 +1741,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579314</v>
+        <v>579436</v>
       </c>
       <c r="R11" t="n">
-        <v>6417689</v>
+        <v>6417634</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1782,6 +1777,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Mkt gammal tall på berget.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125110523</v>
+        <v>125110571</v>
       </c>
       <c r="B12" t="n">
-        <v>91032</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,21 +1825,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1847,12 +1847,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1904,7 +1905,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125110184</v>
+        <v>125110180</v>
       </c>
       <c r="B13" t="n">
-        <v>57761</v>
+        <v>56821</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,25 +1935,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103012</v>
+        <v>100038</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125110297</v>
+        <v>125110184</v>
       </c>
       <c r="B2" t="n">
-        <v>91032</v>
+        <v>57761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -732,7 +733,7 @@
         <v>6417713</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125110495</v>
+        <v>125110671</v>
       </c>
       <c r="B3" t="n">
-        <v>57519</v>
+        <v>57918</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103037</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,7 +827,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579536</v>
+        <v>579247</v>
       </c>
       <c r="R3" t="n">
-        <v>6417623</v>
+        <v>6417660</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,11 +873,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Nu bebott av nötväcka!</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125110184</v>
+        <v>125110359</v>
       </c>
       <c r="B4" t="n">
-        <v>57761</v>
+        <v>57918</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,37 +911,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>103037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -956,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579324</v>
+        <v>579299</v>
       </c>
       <c r="R4" t="n">
-        <v>6417713</v>
+        <v>6417671</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1018,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125110359</v>
+        <v>125110180</v>
       </c>
       <c r="B5" t="n">
-        <v>57918</v>
+        <v>56821</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,20 +1021,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103037</v>
+        <v>100038</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1051,12 +1042,16 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579299</v>
+        <v>579324</v>
       </c>
       <c r="R5" t="n">
-        <v>6417671</v>
+        <v>6417713</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110523</v>
+        <v>125110495</v>
       </c>
       <c r="B6" t="n">
-        <v>91032</v>
+        <v>57519</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,34 +1139,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1179,13 +1171,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579507</v>
+        <v>579536</v>
       </c>
       <c r="R6" t="n">
-        <v>6417672</v>
+        <v>6417623</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,13 +1209,17 @@
           <t>2025-05-15</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Nu bebott av nötväcka!</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1242,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110142</v>
+        <v>125110121</v>
       </c>
       <c r="B7" t="n">
-        <v>57918</v>
+        <v>57761</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,46 +1250,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103037</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 23021, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579356</v>
+        <v>579349</v>
       </c>
       <c r="R7" t="n">
-        <v>6417758</v>
+        <v>6417761</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125110121</v>
+        <v>125110444</v>
       </c>
       <c r="B8" t="n">
-        <v>57761</v>
+        <v>90063</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103012</v>
+        <v>889</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Irpicodon pendulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1390,13 +1390,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1404,10 +1403,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579349</v>
+        <v>579436</v>
       </c>
       <c r="R8" t="n">
-        <v>6417761</v>
+        <v>6417634</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,12 +1441,18 @@
           <t>2025-05-15</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mkt gammal tall på berget.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1466,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125110671</v>
+        <v>125110571</v>
       </c>
       <c r="B9" t="n">
-        <v>57918</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,33 +1483,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103037</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1514,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579247</v>
+        <v>579507</v>
       </c>
       <c r="R9" t="n">
-        <v>6417660</v>
+        <v>6417672</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1576,7 +1585,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110326</v>
+        <v>125110297</v>
       </c>
       <c r="B10" t="n">
         <v>91032</v>
@@ -1627,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579314</v>
+        <v>579324</v>
       </c>
       <c r="R10" t="n">
-        <v>6417689</v>
+        <v>6417713</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110444</v>
+        <v>125110142</v>
       </c>
       <c r="B11" t="n">
-        <v>90063</v>
+        <v>57918</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1702,49 +1711,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>889</v>
+        <v>103037</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Irpicodon pendulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23021, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579436</v>
+        <v>579356</v>
       </c>
       <c r="R11" t="n">
-        <v>6417634</v>
+        <v>6417758</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1779,18 +1785,12 @@
           <t>2025-05-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Mkt gammal tall på berget.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1809,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125110571</v>
+        <v>125110523</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>91032</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,21 +1825,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1847,13 +1847,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1905,6 +1904,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125110180</v>
+        <v>125110326</v>
       </c>
       <c r="B13" t="n">
-        <v>56821</v>
+        <v>91032</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,39 +1935,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100038</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1975,13 +1974,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579324</v>
+        <v>579314</v>
       </c>
       <c r="R13" t="n">
-        <v>6417713</v>
+        <v>6417689</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,6 +2018,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125110184</v>
+        <v>125110671</v>
       </c>
       <c r="B2" t="n">
-        <v>57761</v>
+        <v>57918</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,37 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>103037</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579324</v>
+        <v>579247</v>
       </c>
       <c r="R2" t="n">
-        <v>6417713</v>
+        <v>6417660</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125110671</v>
+        <v>125110184</v>
       </c>
       <c r="B3" t="n">
-        <v>57918</v>
+        <v>57761</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,33 +797,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103037</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579247</v>
+        <v>579324</v>
       </c>
       <c r="R3" t="n">
-        <v>6417660</v>
+        <v>6417713</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125110359</v>
+        <v>125110495</v>
       </c>
       <c r="B4" t="n">
-        <v>57918</v>
+        <v>57519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,7 +937,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579299</v>
+        <v>579536</v>
       </c>
       <c r="R4" t="n">
-        <v>6417671</v>
+        <v>6417623</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,6 +983,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Nu bebott av nötväcka!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125110180</v>
+        <v>125110297</v>
       </c>
       <c r="B5" t="n">
-        <v>56821</v>
+        <v>91032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,39 +1026,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100038</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1067,7 +1071,7 @@
         <v>6417713</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,6 +1109,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110495</v>
+        <v>125110142</v>
       </c>
       <c r="B6" t="n">
-        <v>57519</v>
+        <v>57918</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>103037</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,23 +1166,23 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23021, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579536</v>
+        <v>579356</v>
       </c>
       <c r="R6" t="n">
-        <v>6417623</v>
+        <v>6417758</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,11 +1212,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Nu bebott av nötväcka!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110121</v>
+        <v>125110359</v>
       </c>
       <c r="B7" t="n">
-        <v>57761</v>
+        <v>57918</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,37 +1250,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>103037</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1290,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579349</v>
+        <v>579299</v>
       </c>
       <c r="R7" t="n">
-        <v>6417761</v>
+        <v>6417671</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1352,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125110444</v>
+        <v>125110180</v>
       </c>
       <c r="B8" t="n">
-        <v>90063</v>
+        <v>56821</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,25 +1360,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>889</v>
+        <v>100038</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Irpicodon pendulus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1390,12 +1386,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1403,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579436</v>
+        <v>579324</v>
       </c>
       <c r="R8" t="n">
-        <v>6417634</v>
+        <v>6417713</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,18 +1438,12 @@
           <t>2025-05-15</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Mkt gammal tall på berget.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1585,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110297</v>
+        <v>125110444</v>
       </c>
       <c r="B10" t="n">
-        <v>91032</v>
+        <v>90063</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,31 +1592,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>889</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Irpicodon pendulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1636,13 +1627,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579324</v>
+        <v>579436</v>
       </c>
       <c r="R10" t="n">
-        <v>6417713</v>
+        <v>6417634</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1672,6 +1663,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mkt gammal tall på berget.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110142</v>
+        <v>125110523</v>
       </c>
       <c r="B11" t="n">
-        <v>57918</v>
+        <v>91032</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,46 +1707,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103037</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 23021, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579356</v>
+        <v>579507</v>
       </c>
       <c r="R11" t="n">
-        <v>6417758</v>
+        <v>6417672</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1791,6 +1790,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1809,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125110523</v>
+        <v>125110121</v>
       </c>
       <c r="B12" t="n">
-        <v>91032</v>
+        <v>57761</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,21 +1825,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>103012</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1847,12 +1847,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1860,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579507</v>
+        <v>579349</v>
       </c>
       <c r="R12" t="n">
-        <v>6417672</v>
+        <v>6417761</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1904,7 +1905,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125110671</v>
+        <v>125110180</v>
       </c>
       <c r="B2" t="n">
-        <v>57918</v>
+        <v>56821</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103037</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,12 +708,16 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579247</v>
+        <v>579324</v>
       </c>
       <c r="R2" t="n">
-        <v>6417660</v>
+        <v>6417713</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -1128,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110142</v>
+        <v>125110444</v>
       </c>
       <c r="B6" t="n">
-        <v>57918</v>
+        <v>90063</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,46 +1144,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103037</v>
+        <v>889</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Irpicodon pendulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 23021, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579356</v>
+        <v>579436</v>
       </c>
       <c r="R6" t="n">
-        <v>6417758</v>
+        <v>6417634</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1214,12 +1221,18 @@
           <t>2025-05-15</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Mkt gammal tall på berget.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,7 +1251,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110359</v>
+        <v>125110671</v>
       </c>
       <c r="B7" t="n">
         <v>57918</v>
@@ -1286,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579299</v>
+        <v>579247</v>
       </c>
       <c r="R7" t="n">
-        <v>6417671</v>
+        <v>6417660</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1348,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125110180</v>
+        <v>125110359</v>
       </c>
       <c r="B8" t="n">
-        <v>56821</v>
+        <v>57918</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,20 +1373,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100038</v>
+        <v>103037</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1381,16 +1394,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1400,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579324</v>
+        <v>579299</v>
       </c>
       <c r="R8" t="n">
-        <v>6417713</v>
+        <v>6417671</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1462,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125110571</v>
+        <v>125110523</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>91032</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,21 +1487,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1500,13 +1509,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1558,6 +1566,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1576,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110444</v>
+        <v>125110142</v>
       </c>
       <c r="B10" t="n">
-        <v>90063</v>
+        <v>57918</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,49 +1597,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>889</v>
+        <v>103037</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Irpicodon pendulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23021, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579436</v>
+        <v>579356</v>
       </c>
       <c r="R10" t="n">
-        <v>6417634</v>
+        <v>6417758</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1665,18 +1671,12 @@
           <t>2025-05-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mkt gammal tall på berget.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110523</v>
+        <v>125110326</v>
       </c>
       <c r="B11" t="n">
         <v>91032</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1746,13 +1746,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579507</v>
+        <v>579314</v>
       </c>
       <c r="R11" t="n">
-        <v>6417672</v>
+        <v>6417689</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125110121</v>
+        <v>125110571</v>
       </c>
       <c r="B12" t="n">
-        <v>57761</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,21 +1825,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1851,7 +1851,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579349</v>
+        <v>579507</v>
       </c>
       <c r="R12" t="n">
-        <v>6417761</v>
+        <v>6417672</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125110326</v>
+        <v>125110121</v>
       </c>
       <c r="B13" t="n">
-        <v>91032</v>
+        <v>57761</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,34 +1939,35 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>103012</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1974,13 +1975,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579314</v>
+        <v>579349</v>
       </c>
       <c r="R13" t="n">
-        <v>6417689</v>
+        <v>6417761</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2018,7 +2019,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125110180</v>
+        <v>125110444</v>
       </c>
       <c r="B2" t="n">
-        <v>56821</v>
+        <v>90063</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100038</v>
+        <v>889</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Irpicodon pendulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,13 +713,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579324</v>
+        <v>579436</v>
       </c>
       <c r="R2" t="n">
-        <v>6417713</v>
+        <v>6417634</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -765,12 +764,18 @@
           <t>2025-05-15</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mkt gammal tall på berget.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125110184</v>
+        <v>125110523</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>91032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,13 +832,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579324</v>
+        <v>579507</v>
       </c>
       <c r="R3" t="n">
-        <v>6417713</v>
+        <v>6417672</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,6 +889,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125110495</v>
+        <v>125110571</v>
       </c>
       <c r="B4" t="n">
-        <v>57519</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,16 +924,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -936,12 +941,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -951,13 +960,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579536</v>
+        <v>579507</v>
       </c>
       <c r="R4" t="n">
-        <v>6417623</v>
+        <v>6417672</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,11 +996,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Nu bebott av nötväcka!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125110297</v>
+        <v>125110180</v>
       </c>
       <c r="B5" t="n">
-        <v>91032</v>
+        <v>56821</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,38 +1034,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>100038</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1075,7 +1080,7 @@
         <v>6417713</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,7 +1118,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1132,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110444</v>
+        <v>125110297</v>
       </c>
       <c r="B6" t="n">
-        <v>90063</v>
+        <v>91032</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,31 +1152,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>889</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Irpicodon pendulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1183,13 +1187,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579436</v>
+        <v>579324</v>
       </c>
       <c r="R6" t="n">
-        <v>6417634</v>
+        <v>6417713</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,11 +1223,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Mkt gammal tall på berget.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1361,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125110359</v>
+        <v>125110495</v>
       </c>
       <c r="B8" t="n">
-        <v>57918</v>
+        <v>57519</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,25 +1372,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103037</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1399,7 +1398,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1409,13 +1408,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579299</v>
+        <v>579536</v>
       </c>
       <c r="R8" t="n">
-        <v>6417671</v>
+        <v>6417623</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,6 +1444,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Nu bebott av nötväcka!</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,7 +1475,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125110523</v>
+        <v>125110326</v>
       </c>
       <c r="B9" t="n">
         <v>91032</v>
@@ -1506,7 +1510,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1522,13 +1526,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579507</v>
+        <v>579314</v>
       </c>
       <c r="R9" t="n">
-        <v>6417672</v>
+        <v>6417689</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1585,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110142</v>
+        <v>125110121</v>
       </c>
       <c r="B10" t="n">
-        <v>57918</v>
+        <v>57761</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,46 +1601,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103037</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 23021, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579356</v>
+        <v>579349</v>
       </c>
       <c r="R10" t="n">
-        <v>6417758</v>
+        <v>6417761</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1695,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110326</v>
+        <v>125110359</v>
       </c>
       <c r="B11" t="n">
-        <v>91032</v>
+        <v>57918</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1707,38 +1715,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>103037</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1746,13 +1751,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579314</v>
+        <v>579299</v>
       </c>
       <c r="R11" t="n">
-        <v>6417689</v>
+        <v>6417671</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1790,7 +1795,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1809,10 +1813,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125110571</v>
+        <v>125110142</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>57918</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,50 +1825,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103037</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23021, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579507</v>
+        <v>579356</v>
       </c>
       <c r="R12" t="n">
-        <v>6417672</v>
+        <v>6417758</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1923,7 +1923,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125110121</v>
+        <v>125110184</v>
       </c>
       <c r="B13" t="n">
         <v>57761</v>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579349</v>
+        <v>579324</v>
       </c>
       <c r="R13" t="n">
-        <v>6417761</v>
+        <v>6417713</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1022,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125110180</v>
+        <v>125110297</v>
       </c>
       <c r="B5" t="n">
-        <v>56821</v>
+        <v>91032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,39 +1034,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100038</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1080,7 +1079,7 @@
         <v>6417713</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,6 +1117,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110297</v>
+        <v>125110671</v>
       </c>
       <c r="B6" t="n">
-        <v>91032</v>
+        <v>57918</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,38 +1148,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>103037</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1187,13 +1184,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579324</v>
+        <v>579247</v>
       </c>
       <c r="R6" t="n">
-        <v>6417713</v>
+        <v>6417660</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1231,7 +1228,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1250,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110671</v>
+        <v>125110180</v>
       </c>
       <c r="B7" t="n">
-        <v>57918</v>
+        <v>56821</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,20 +1258,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103037</v>
+        <v>100038</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1283,12 +1279,16 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579247</v>
+        <v>579324</v>
       </c>
       <c r="R7" t="n">
-        <v>6417660</v>
+        <v>6417713</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1475,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125110326</v>
+        <v>125110121</v>
       </c>
       <c r="B9" t="n">
-        <v>91032</v>
+        <v>57761</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,34 +1491,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1526,13 +1527,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579314</v>
+        <v>579349</v>
       </c>
       <c r="R9" t="n">
-        <v>6417689</v>
+        <v>6417761</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1570,7 +1571,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1589,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110121</v>
+        <v>125110326</v>
       </c>
       <c r="B10" t="n">
-        <v>57761</v>
+        <v>91032</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,35 +1605,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103012</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1641,13 +1640,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579349</v>
+        <v>579314</v>
       </c>
       <c r="R10" t="n">
-        <v>6417761</v>
+        <v>6417689</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1685,6 +1684,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125110444</v>
+        <v>125110571</v>
       </c>
       <c r="B2" t="n">
-        <v>90063</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>889</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Irpicodon pendulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,12 +713,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579436</v>
+        <v>579507</v>
       </c>
       <c r="R2" t="n">
-        <v>6417634</v>
+        <v>6417672</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,18 +765,12 @@
           <t>2025-05-15</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Mkt gammal tall på berget.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125110523</v>
+        <v>125110142</v>
       </c>
       <c r="B3" t="n">
-        <v>91032</v>
+        <v>57918</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,49 +801,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>103037</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23021, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579507</v>
+        <v>579356</v>
       </c>
       <c r="R3" t="n">
-        <v>6417672</v>
+        <v>6417758</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125110571</v>
+        <v>125110444</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>90063</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>889</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Irpicodon pendulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -946,13 +937,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -960,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579507</v>
+        <v>579436</v>
       </c>
       <c r="R4" t="n">
-        <v>6417672</v>
+        <v>6417634</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,12 +988,18 @@
           <t>2025-05-15</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mkt gammal tall på berget.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1022,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125110297</v>
+        <v>125110121</v>
       </c>
       <c r="B5" t="n">
-        <v>91032</v>
+        <v>57761</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,34 +1034,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1073,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579324</v>
+        <v>579349</v>
       </c>
       <c r="R5" t="n">
-        <v>6417713</v>
+        <v>6417761</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,7 +1114,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1246,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110180</v>
+        <v>125110523</v>
       </c>
       <c r="B7" t="n">
-        <v>56821</v>
+        <v>91032</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,25 +1254,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100038</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1284,13 +1280,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1298,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579324</v>
+        <v>579507</v>
       </c>
       <c r="R7" t="n">
-        <v>6417713</v>
+        <v>6417672</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1342,6 +1337,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1360,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125110495</v>
+        <v>125110180</v>
       </c>
       <c r="B8" t="n">
-        <v>57519</v>
+        <v>56821</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,33 +1368,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>100038</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1408,13 +1408,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579536</v>
+        <v>579324</v>
       </c>
       <c r="R8" t="n">
-        <v>6417623</v>
+        <v>6417713</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,11 +1444,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Nu bebott av nötväcka!</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125110121</v>
+        <v>125110495</v>
       </c>
       <c r="B9" t="n">
-        <v>57761</v>
+        <v>57519</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,33 +1486,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103012</v>
+        <v>100048</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1527,13 +1518,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579349</v>
+        <v>579536</v>
       </c>
       <c r="R9" t="n">
-        <v>6417761</v>
+        <v>6417623</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1563,6 +1554,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Nu bebott av nötväcka!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110326</v>
+        <v>125110184</v>
       </c>
       <c r="B10" t="n">
-        <v>91032</v>
+        <v>57761</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,34 +1601,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1640,13 +1637,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579314</v>
+        <v>579324</v>
       </c>
       <c r="R10" t="n">
-        <v>6417689</v>
+        <v>6417713</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1684,7 +1681,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1703,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110359</v>
+        <v>125110326</v>
       </c>
       <c r="B11" t="n">
-        <v>57918</v>
+        <v>91032</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,35 +1711,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103037</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1751,13 +1750,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579299</v>
+        <v>579314</v>
       </c>
       <c r="R11" t="n">
-        <v>6417671</v>
+        <v>6417689</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1795,6 +1794,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1813,7 +1813,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125110142</v>
+        <v>125110359</v>
       </c>
       <c r="B12" t="n">
         <v>57918</v>
@@ -1857,14 +1857,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 23021, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579356</v>
+        <v>579299</v>
       </c>
       <c r="R12" t="n">
-        <v>6417758</v>
+        <v>6417671</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125110184</v>
+        <v>125110297</v>
       </c>
       <c r="B13" t="n">
-        <v>57761</v>
+        <v>91032</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,35 +1939,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103012</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1981,7 +1980,7 @@
         <v>6417713</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,6 +2018,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125110495</v>
+        <v>125110184</v>
       </c>
       <c r="B9" t="n">
-        <v>57519</v>
+        <v>57761</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,29 +1486,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100048</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1518,13 +1522,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579536</v>
+        <v>579324</v>
       </c>
       <c r="R9" t="n">
-        <v>6417623</v>
+        <v>6417713</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1554,11 +1558,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Nu bebott av nötväcka!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110184</v>
+        <v>125110495</v>
       </c>
       <c r="B10" t="n">
-        <v>57761</v>
+        <v>57519</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,33 +1600,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103012</v>
+        <v>100048</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1637,13 +1632,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579324</v>
+        <v>579536</v>
       </c>
       <c r="R10" t="n">
-        <v>6417713</v>
+        <v>6417623</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,6 +1668,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Nu bebott av nötväcka!</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110326</v>
+        <v>125110359</v>
       </c>
       <c r="B11" t="n">
-        <v>91032</v>
+        <v>57918</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,38 +1711,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>103037</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1750,13 +1747,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579314</v>
+        <v>579299</v>
       </c>
       <c r="R11" t="n">
-        <v>6417689</v>
+        <v>6417671</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1794,7 +1791,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1813,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125110359</v>
+        <v>125110326</v>
       </c>
       <c r="B12" t="n">
-        <v>57918</v>
+        <v>91032</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,35 +1821,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103037</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1861,13 +1860,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579299</v>
+        <v>579314</v>
       </c>
       <c r="R12" t="n">
-        <v>6417671</v>
+        <v>6417689</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1905,6 +1904,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125110571</v>
+        <v>125110523</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>91032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,13 +713,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -771,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125110142</v>
+        <v>125110444</v>
       </c>
       <c r="B3" t="n">
-        <v>57918</v>
+        <v>90063</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,46 +801,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103037</v>
+        <v>889</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Irpicodon pendulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 23021, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579356</v>
+        <v>579436</v>
       </c>
       <c r="R3" t="n">
-        <v>6417758</v>
+        <v>6417634</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -875,12 +878,18 @@
           <t>2025-05-15</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mkt gammal tall på berget.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125110444</v>
+        <v>125110671</v>
       </c>
       <c r="B4" t="n">
-        <v>90063</v>
+        <v>57918</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +920,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>889</v>
+        <v>103037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Irpicodon pendulus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579436</v>
+        <v>579247</v>
       </c>
       <c r="R4" t="n">
-        <v>6417634</v>
+        <v>6417660</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,18 +994,12 @@
           <t>2025-05-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Mkt gammal tall på berget.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110671</v>
+        <v>125110326</v>
       </c>
       <c r="B6" t="n">
-        <v>57918</v>
+        <v>91032</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,35 +1144,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103037</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,13 +1183,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579247</v>
+        <v>579314</v>
       </c>
       <c r="R6" t="n">
-        <v>6417660</v>
+        <v>6417689</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,6 +1227,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1242,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110523</v>
+        <v>125110184</v>
       </c>
       <c r="B7" t="n">
-        <v>91032</v>
+        <v>57761</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,21 +1262,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1280,12 +1284,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1293,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579507</v>
+        <v>579324</v>
       </c>
       <c r="R7" t="n">
-        <v>6417672</v>
+        <v>6417713</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1337,7 +1342,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1470,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125110184</v>
+        <v>125110571</v>
       </c>
       <c r="B9" t="n">
-        <v>57761</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,21 +1490,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1512,7 +1516,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1522,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579324</v>
+        <v>579507</v>
       </c>
       <c r="R9" t="n">
-        <v>6417713</v>
+        <v>6417672</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1584,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110495</v>
+        <v>125110142</v>
       </c>
       <c r="B10" t="n">
-        <v>57519</v>
+        <v>57918</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,25 +1600,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>103037</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1622,23 +1626,23 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23021, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579536</v>
+        <v>579356</v>
       </c>
       <c r="R10" t="n">
-        <v>6417623</v>
+        <v>6417758</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,11 +1672,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Nu bebott av nötväcka!</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110359</v>
+        <v>125110495</v>
       </c>
       <c r="B11" t="n">
-        <v>57918</v>
+        <v>57519</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,25 +1710,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103037</v>
+        <v>100048</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1737,7 +1736,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1747,13 +1746,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579299</v>
+        <v>579536</v>
       </c>
       <c r="R11" t="n">
-        <v>6417671</v>
+        <v>6417623</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1783,6 +1782,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Nu bebott av nötväcka!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,7 +1813,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125110326</v>
+        <v>125110297</v>
       </c>
       <c r="B12" t="n">
         <v>91032</v>
@@ -1860,10 +1864,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579314</v>
+        <v>579324</v>
       </c>
       <c r="R12" t="n">
-        <v>6417689</v>
+        <v>6417713</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1923,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125110297</v>
+        <v>125110359</v>
       </c>
       <c r="B13" t="n">
-        <v>91032</v>
+        <v>57918</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,38 +1939,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>103037</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1974,13 +1975,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579324</v>
+        <v>579299</v>
       </c>
       <c r="R13" t="n">
-        <v>6417713</v>
+        <v>6417671</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2018,7 +2019,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125110523</v>
+        <v>125110671</v>
       </c>
       <c r="B2" t="n">
-        <v>91032</v>
+        <v>58026</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>103037</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579507</v>
+        <v>579247</v>
       </c>
       <c r="R2" t="n">
-        <v>6417672</v>
+        <v>6417660</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -770,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125110444</v>
+        <v>125110297</v>
       </c>
       <c r="B3" t="n">
-        <v>90063</v>
+        <v>91186</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,31 +801,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>889</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Irpicodon pendulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -840,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579436</v>
+        <v>579324</v>
       </c>
       <c r="R3" t="n">
-        <v>6417634</v>
+        <v>6417713</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,11 +872,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Mkt gammal tall på berget.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125110671</v>
+        <v>125110184</v>
       </c>
       <c r="B4" t="n">
-        <v>57918</v>
+        <v>57914</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,33 +911,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -956,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579247</v>
+        <v>579324</v>
       </c>
       <c r="R4" t="n">
-        <v>6417660</v>
+        <v>6417713</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1018,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125110121</v>
+        <v>125110326</v>
       </c>
       <c r="B5" t="n">
-        <v>57761</v>
+        <v>91186</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,35 +1029,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,13 +1064,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579349</v>
+        <v>579314</v>
       </c>
       <c r="R5" t="n">
-        <v>6417761</v>
+        <v>6417689</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,6 +1108,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1132,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110326</v>
+        <v>125110444</v>
       </c>
       <c r="B6" t="n">
-        <v>91032</v>
+        <v>90216</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,31 +1143,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>889</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Irpicodon pendulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1183,13 +1178,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579314</v>
+        <v>579436</v>
       </c>
       <c r="R6" t="n">
-        <v>6417689</v>
+        <v>6417634</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,6 +1214,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Mkt gammal tall på berget.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,10 +1246,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110184</v>
+        <v>125110121</v>
       </c>
       <c r="B7" t="n">
-        <v>57761</v>
+        <v>57914</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579324</v>
+        <v>579349</v>
       </c>
       <c r="R7" t="n">
-        <v>6417713</v>
+        <v>6417761</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1363,7 +1363,7 @@
         <v>125110180</v>
       </c>
       <c r="B8" t="n">
-        <v>56821</v>
+        <v>56939</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125110571</v>
+        <v>125110142</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>58026</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,50 +1486,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103037</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23021, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579507</v>
+        <v>579356</v>
       </c>
       <c r="R9" t="n">
-        <v>6417672</v>
+        <v>6417758</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1588,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110142</v>
+        <v>125110571</v>
       </c>
       <c r="B10" t="n">
-        <v>57918</v>
+        <v>57632</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,46 +1596,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103037</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>A 23021, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579356</v>
+        <v>579507</v>
       </c>
       <c r="R10" t="n">
-        <v>6417758</v>
+        <v>6417672</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1701,7 +1701,7 @@
         <v>125110495</v>
       </c>
       <c r="B11" t="n">
-        <v>57519</v>
+        <v>57648</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1813,10 +1813,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125110297</v>
+        <v>125110523</v>
       </c>
       <c r="B12" t="n">
-        <v>91032</v>
+        <v>91186</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1864,13 +1864,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579324</v>
+        <v>579507</v>
       </c>
       <c r="R12" t="n">
-        <v>6417713</v>
+        <v>6417672</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>125110359</v>
       </c>
       <c r="B13" t="n">
-        <v>57918</v>
+        <v>58026</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125110671</v>
+        <v>125110142</v>
       </c>
       <c r="B2" t="n">
         <v>58026</v>
@@ -719,14 +719,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23021, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579247</v>
+        <v>579356</v>
       </c>
       <c r="R2" t="n">
-        <v>6417660</v>
+        <v>6417758</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125110297</v>
+        <v>125110671</v>
       </c>
       <c r="B3" t="n">
-        <v>91186</v>
+        <v>58026</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,38 +797,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>103037</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579324</v>
+        <v>579247</v>
       </c>
       <c r="R3" t="n">
-        <v>6417713</v>
+        <v>6417660</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +877,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125110184</v>
+        <v>125110495</v>
       </c>
       <c r="B4" t="n">
-        <v>57914</v>
+        <v>57648</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,33 +911,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -951,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579324</v>
+        <v>579536</v>
       </c>
       <c r="R4" t="n">
-        <v>6417713</v>
+        <v>6417623</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,6 +979,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Nu bebott av nötväcka!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125110326</v>
+        <v>125110180</v>
       </c>
       <c r="B5" t="n">
-        <v>91186</v>
+        <v>56939</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,38 +1022,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>100038</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1064,13 +1062,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579314</v>
+        <v>579324</v>
       </c>
       <c r="R5" t="n">
-        <v>6417689</v>
+        <v>6417713</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,7 +1106,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110444</v>
+        <v>125110326</v>
       </c>
       <c r="B6" t="n">
-        <v>90216</v>
+        <v>91186</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,31 +1140,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>889</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Irpicodon pendulus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1178,13 +1175,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579436</v>
+        <v>579314</v>
       </c>
       <c r="R6" t="n">
-        <v>6417634</v>
+        <v>6417689</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,11 +1211,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Mkt gammal tall på berget.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110121</v>
+        <v>125110359</v>
       </c>
       <c r="B7" t="n">
-        <v>57914</v>
+        <v>58026</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,37 +1250,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>103037</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1298,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579349</v>
+        <v>579299</v>
       </c>
       <c r="R7" t="n">
-        <v>6417761</v>
+        <v>6417671</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1360,10 +1348,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125110180</v>
+        <v>125110571</v>
       </c>
       <c r="B8" t="n">
-        <v>56939</v>
+        <v>57632</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,25 +1360,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100038</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1402,7 +1390,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1412,10 +1400,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579324</v>
+        <v>579507</v>
       </c>
       <c r="R8" t="n">
-        <v>6417713</v>
+        <v>6417672</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1474,10 +1462,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125110142</v>
+        <v>125110121</v>
       </c>
       <c r="B9" t="n">
-        <v>58026</v>
+        <v>57914</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,46 +1474,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103037</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 23021, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579356</v>
+        <v>579349</v>
       </c>
       <c r="R9" t="n">
-        <v>6417758</v>
+        <v>6417761</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1584,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110571</v>
+        <v>125110184</v>
       </c>
       <c r="B10" t="n">
-        <v>57632</v>
+        <v>57914</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103012</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1626,7 +1618,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1636,10 +1628,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579507</v>
+        <v>579324</v>
       </c>
       <c r="R10" t="n">
-        <v>6417672</v>
+        <v>6417713</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1698,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110495</v>
+        <v>125110444</v>
       </c>
       <c r="B11" t="n">
-        <v>57648</v>
+        <v>90216</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,31 +1706,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100048</v>
+        <v>889</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Irpicodon pendulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1746,13 +1741,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579536</v>
+        <v>579436</v>
       </c>
       <c r="R11" t="n">
-        <v>6417623</v>
+        <v>6417634</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1786,7 +1781,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Nu bebott av nötväcka!</t>
+          <t>Mkt gammal tall på berget.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,6 +1790,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1927,10 +1923,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125110359</v>
+        <v>125110297</v>
       </c>
       <c r="B13" t="n">
-        <v>58026</v>
+        <v>91186</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,35 +1935,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103037</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1975,13 +1974,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579299</v>
+        <v>579324</v>
       </c>
       <c r="R13" t="n">
-        <v>6417671</v>
+        <v>6417713</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,6 +2018,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110326</v>
+        <v>125110359</v>
       </c>
       <c r="B6" t="n">
-        <v>91186</v>
+        <v>58026</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,38 +1136,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>103037</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1175,13 +1172,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579314</v>
+        <v>579299</v>
       </c>
       <c r="R6" t="n">
-        <v>6417689</v>
+        <v>6417671</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1219,7 +1216,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,10 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110359</v>
+        <v>125110326</v>
       </c>
       <c r="B7" t="n">
-        <v>58026</v>
+        <v>91186</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,35 +1246,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103037</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1286,13 +1285,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579299</v>
+        <v>579314</v>
       </c>
       <c r="R7" t="n">
-        <v>6417671</v>
+        <v>6417689</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,6 +1329,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -675,58 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125110142</v>
+        <v>125110121</v>
       </c>
       <c r="B2" t="n">
-        <v>58026</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103037</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 23021, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579356</v>
+        <v>579349</v>
       </c>
       <c r="R2" t="n">
-        <v>6417758</v>
+        <v>6417761</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -785,47 +784,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125110671</v>
+        <v>125110523</v>
       </c>
       <c r="B3" t="n">
-        <v>58026</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91240</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103037</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579247</v>
+        <v>579507</v>
       </c>
       <c r="R3" t="n">
-        <v>6417660</v>
+        <v>6417672</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,6 +874,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,37 +893,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125110495</v>
+        <v>125110359</v>
       </c>
       <c r="B4" t="n">
-        <v>57648</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>103037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,7 +926,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>bo, hörda ungar</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -943,13 +936,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579536</v>
+        <v>579299</v>
       </c>
       <c r="R4" t="n">
-        <v>6417623</v>
+        <v>6417671</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Nu bebott av nötväcka!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,37 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125110180</v>
+        <v>125110184</v>
       </c>
       <c r="B5" t="n">
-        <v>56939</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100038</v>
+        <v>103012</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1124,15 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110359</v>
+        <v>125110671</v>
       </c>
       <c r="B6" t="n">
-        <v>58026</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579299</v>
+        <v>579247</v>
       </c>
       <c r="R6" t="n">
-        <v>6417671</v>
+        <v>6417660</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1234,15 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110326</v>
+        <v>125110297</v>
       </c>
       <c r="B7" t="n">
-        <v>91186</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91240</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1285,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579314</v>
+        <v>579324</v>
       </c>
       <c r="R7" t="n">
-        <v>6417689</v>
+        <v>6417713</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,15 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125110571</v>
+        <v>125110326</v>
       </c>
       <c r="B8" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91240</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,35 +1332,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1400,13 +1367,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579507</v>
+        <v>579314</v>
       </c>
       <c r="R8" t="n">
-        <v>6417672</v>
+        <v>6417689</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,6 +1411,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1462,15 +1430,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125110121</v>
+        <v>125110571</v>
       </c>
       <c r="B9" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,21 +1441,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1504,7 +1467,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1514,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579349</v>
+        <v>579507</v>
       </c>
       <c r="R9" t="n">
-        <v>6417761</v>
+        <v>6417672</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1576,15 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110184</v>
+        <v>125110444</v>
       </c>
       <c r="B10" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,21 +1550,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103012</v>
+        <v>889</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Irpicodon pendulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1614,13 +1572,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1628,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579324</v>
+        <v>579436</v>
       </c>
       <c r="R10" t="n">
-        <v>6417713</v>
+        <v>6417634</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,12 +1623,18 @@
           <t>2025-05-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mkt gammal tall på berget.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1690,15 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110444</v>
+        <v>125110495</v>
       </c>
       <c r="B11" t="n">
-        <v>90216</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57664</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,34 +1664,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>889</v>
+        <v>100048</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Irpicodon pendulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1741,13 +1696,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579436</v>
+        <v>579536</v>
       </c>
       <c r="R11" t="n">
-        <v>6417634</v>
+        <v>6417623</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,7 +1736,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Mkt gammal tall på berget.</t>
+          <t>Nu bebott av nötväcka!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,7 +1745,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1809,61 +1763,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125110523</v>
+        <v>125110142</v>
       </c>
       <c r="B12" t="n">
-        <v>91186</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>103037</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23021, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579507</v>
+        <v>579356</v>
       </c>
       <c r="R12" t="n">
-        <v>6417672</v>
+        <v>6417758</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1904,7 +1850,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1923,50 +1868,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125110297</v>
+        <v>125110180</v>
       </c>
       <c r="B13" t="n">
-        <v>91186</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56947</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>100038</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1980,7 +1921,7 @@
         <v>6417713</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2018,7 +1959,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1975,6 +1975,1734 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128948895</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 23022, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>579414</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6417702</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128948436</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92269</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>366</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Artomyces pyxidatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 23021, Häckenstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>579353</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6417752</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128948462</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 23021, Häckenstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>579338</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6417742</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Födosöksspår</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128948924</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92269</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>366</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Artomyces pyxidatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 23021, Häckenstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>579284</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6417717</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128948686</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92269</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>366</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Artomyces pyxidatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 23021, Häckenstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>579336</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6417683</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128948597</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57729</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 23021, Häckenstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>579324</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6417730</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Svarade på uppspelning.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128948980</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 23021, Häckenstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>579267</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6417704</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128948733</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 23021, Häckenstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>579363</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6417668</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128948660</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 23021, Häckenstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>579336</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6417683</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128948844</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 23022, Häckenstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>579382</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6417694</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128948753</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57874</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A 23021, Häckenstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>579456</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6417686</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128948485</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92269</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>366</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Artomyces pyxidatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>A 23021, Häckenstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>579339</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6417733</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128950752</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91716</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>A 23021, Häckenstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>579338</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6417689</v>
+      </c>
+      <c r="S26" t="n">
+        <v>75</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128949214</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92304</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hericium coralloides</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>A 23021, Häckenstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>579338</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6417689</v>
+      </c>
+      <c r="S27" t="n">
+        <v>75</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128948737</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92475</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4786</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mandelriska</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lactifluus volemus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Kuntze</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>A 23021, Häckenstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>579363</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6417668</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128948452</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92269</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>366</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Artomyces pyxidatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>A 23021, Häckenstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>579338</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6417742</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1980,7 +1980,7 @@
         <v>128948895</v>
       </c>
       <c r="B14" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>128948436</v>
       </c>
       <c r="B15" t="n">
-        <v>92269</v>
+        <v>92273</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>128948462</v>
       </c>
       <c r="B16" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>128948924</v>
       </c>
       <c r="B17" t="n">
-        <v>92269</v>
+        <v>92273</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>128948686</v>
       </c>
       <c r="B18" t="n">
-        <v>92269</v>
+        <v>92273</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>128948597</v>
       </c>
       <c r="B19" t="n">
-        <v>57729</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>128948980</v>
       </c>
       <c r="B20" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>128948733</v>
       </c>
       <c r="B21" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>128948660</v>
       </c>
       <c r="B22" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>128948844</v>
       </c>
       <c r="B23" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128948753</v>
+        <v>128948485</v>
       </c>
       <c r="B24" t="n">
-        <v>57874</v>
+        <v>92273</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3069,35 +3069,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103020</v>
+        <v>366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3105,13 +3100,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579456</v>
+        <v>579339</v>
       </c>
       <c r="R24" t="n">
-        <v>6417686</v>
+        <v>6417733</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3149,6 +3144,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3167,10 +3163,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128948485</v>
+        <v>128948753</v>
       </c>
       <c r="B25" t="n">
-        <v>92269</v>
+        <v>57878</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3178,30 +3174,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>366</v>
+        <v>103020</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3209,13 +3210,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579339</v>
+        <v>579456</v>
       </c>
       <c r="R25" t="n">
-        <v>6417733</v>
+        <v>6417686</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3253,7 +3254,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>128950752</v>
       </c>
       <c r="B26" t="n">
-        <v>91716</v>
+        <v>91720</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3381,42 +3381,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128949214</v>
+        <v>128948737</v>
       </c>
       <c r="B27" t="n">
-        <v>92304</v>
+        <v>92479</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2014</v>
+        <v>4786</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Kuntze</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3427,13 +3423,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>579338</v>
+        <v>579363</v>
       </c>
       <c r="R27" t="n">
-        <v>6417689</v>
+        <v>6417668</v>
       </c>
       <c r="S27" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3463,11 +3459,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3495,38 +3486,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128948737</v>
+        <v>128949214</v>
       </c>
       <c r="B28" t="n">
-        <v>92475</v>
+        <v>92308</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4786</v>
+        <v>2014</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kuntze</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3537,13 +3532,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579363</v>
+        <v>579338</v>
       </c>
       <c r="R28" t="n">
-        <v>6417668</v>
+        <v>6417689</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3573,6 +3568,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,7 +3603,7 @@
         <v>128948452</v>
       </c>
       <c r="B29" t="n">
-        <v>92269</v>
+        <v>92273</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128948895</v>
+        <v>128948436</v>
       </c>
       <c r="B14" t="n">
-        <v>57717</v>
+        <v>92273</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,49 +1988,44 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 23022, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579414</v>
+        <v>579353</v>
       </c>
       <c r="R14" t="n">
-        <v>6417702</v>
+        <v>6417752</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2068,6 +2063,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128948436</v>
+        <v>128948895</v>
       </c>
       <c r="B15" t="n">
-        <v>92273</v>
+        <v>57717</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,44 +2093,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>366</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23022, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579353</v>
+        <v>579414</v>
       </c>
       <c r="R15" t="n">
-        <v>6417752</v>
+        <v>6417702</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2172,7 +2173,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128948660</v>
+        <v>128948844</v>
       </c>
       <c r="B22" t="n">
         <v>57717</v>
@@ -2872,28 +2872,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23022, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579336</v>
+        <v>579382</v>
       </c>
       <c r="R22" t="n">
-        <v>6417683</v>
+        <v>6417694</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2949,7 +2953,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128948844</v>
+        <v>128948660</v>
       </c>
       <c r="B23" t="n">
         <v>57717</v>
@@ -2977,32 +2981,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 23022, Häckenstad, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>579382</v>
+        <v>579336</v>
       </c>
       <c r="R23" t="n">
-        <v>6417694</v>
+        <v>6417683</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128948485</v>
+        <v>128948753</v>
       </c>
       <c r="B24" t="n">
-        <v>92273</v>
+        <v>57878</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3069,30 +3069,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>366</v>
+        <v>103020</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3100,13 +3105,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579339</v>
+        <v>579456</v>
       </c>
       <c r="R24" t="n">
-        <v>6417733</v>
+        <v>6417686</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3144,7 +3149,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3163,10 +3167,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128948753</v>
+        <v>128948485</v>
       </c>
       <c r="B25" t="n">
-        <v>57878</v>
+        <v>92273</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3174,35 +3178,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103020</v>
+        <v>366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3210,13 +3209,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579456</v>
+        <v>579339</v>
       </c>
       <c r="R25" t="n">
-        <v>6417686</v>
+        <v>6417733</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3254,6 +3253,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3381,32 +3381,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128948737</v>
+        <v>128948452</v>
       </c>
       <c r="B27" t="n">
-        <v>92479</v>
+        <v>92273</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4786</v>
+        <v>366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kuntze</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3423,13 +3423,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>579363</v>
+        <v>579338</v>
       </c>
       <c r="R27" t="n">
-        <v>6417668</v>
+        <v>6417742</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3486,42 +3486,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128949214</v>
+        <v>128948737</v>
       </c>
       <c r="B28" t="n">
-        <v>92308</v>
+        <v>92479</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2014</v>
+        <v>4786</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Kuntze</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3532,13 +3528,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579338</v>
+        <v>579363</v>
       </c>
       <c r="R28" t="n">
-        <v>6417689</v>
+        <v>6417668</v>
       </c>
       <c r="S28" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3568,11 +3564,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3600,10 +3591,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128948452</v>
+        <v>128949214</v>
       </c>
       <c r="B29" t="n">
-        <v>92273</v>
+        <v>92308</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3611,27 +3602,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>366</v>
+        <v>2014</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -3645,10 +3640,10 @@
         <v>579338</v>
       </c>
       <c r="R29" t="n">
-        <v>6417742</v>
+        <v>6417689</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3678,6 +3673,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128948436</v>
+        <v>128948895</v>
       </c>
       <c r="B14" t="n">
-        <v>92273</v>
+        <v>57717</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,44 +1988,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>366</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23022, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579353</v>
+        <v>579414</v>
       </c>
       <c r="R14" t="n">
-        <v>6417752</v>
+        <v>6417702</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2063,7 +2068,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2082,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128948895</v>
+        <v>128948436</v>
       </c>
       <c r="B15" t="n">
-        <v>57717</v>
+        <v>92273</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,49 +2097,44 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 23022, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579414</v>
+        <v>579353</v>
       </c>
       <c r="R15" t="n">
-        <v>6417702</v>
+        <v>6417752</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2173,6 +2172,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128948844</v>
+        <v>128948660</v>
       </c>
       <c r="B22" t="n">
         <v>57717</v>
@@ -2872,32 +2872,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 23022, Häckenstad, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579382</v>
+        <v>579336</v>
       </c>
       <c r="R22" t="n">
-        <v>6417694</v>
+        <v>6417683</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2953,7 +2949,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128948660</v>
+        <v>128948844</v>
       </c>
       <c r="B23" t="n">
         <v>57717</v>
@@ -2981,28 +2977,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23022, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>579336</v>
+        <v>579382</v>
       </c>
       <c r="R23" t="n">
-        <v>6417683</v>
+        <v>6417694</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128948753</v>
+        <v>128948485</v>
       </c>
       <c r="B24" t="n">
-        <v>57878</v>
+        <v>92273</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3069,35 +3069,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103020</v>
+        <v>366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3105,13 +3100,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579456</v>
+        <v>579339</v>
       </c>
       <c r="R24" t="n">
-        <v>6417686</v>
+        <v>6417733</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3149,6 +3144,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3167,10 +3163,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128948485</v>
+        <v>128948753</v>
       </c>
       <c r="B25" t="n">
-        <v>92273</v>
+        <v>57878</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3178,30 +3174,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>366</v>
+        <v>103020</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3209,13 +3210,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579339</v>
+        <v>579456</v>
       </c>
       <c r="R25" t="n">
-        <v>6417733</v>
+        <v>6417686</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3253,7 +3254,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3486,38 +3486,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128948737</v>
+        <v>128949214</v>
       </c>
       <c r="B28" t="n">
-        <v>92479</v>
+        <v>92308</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4786</v>
+        <v>2014</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kuntze</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3528,13 +3532,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579363</v>
+        <v>579338</v>
       </c>
       <c r="R28" t="n">
-        <v>6417668</v>
+        <v>6417689</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3564,6 +3568,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3591,42 +3600,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128949214</v>
+        <v>128948737</v>
       </c>
       <c r="B29" t="n">
-        <v>92308</v>
+        <v>92479</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2014</v>
+        <v>4786</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Kuntze</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -3637,13 +3642,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579338</v>
+        <v>579363</v>
       </c>
       <c r="R29" t="n">
-        <v>6417689</v>
+        <v>6417668</v>
       </c>
       <c r="S29" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3673,11 +3678,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128948895</v>
+        <v>128948436</v>
       </c>
       <c r="B14" t="n">
-        <v>57717</v>
+        <v>92278</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,49 +1988,44 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 23022, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579414</v>
+        <v>579353</v>
       </c>
       <c r="R14" t="n">
-        <v>6417702</v>
+        <v>6417752</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2068,6 +2063,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128948436</v>
+        <v>128948895</v>
       </c>
       <c r="B15" t="n">
-        <v>92273</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,44 +2093,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>366</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23022, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579353</v>
+        <v>579414</v>
       </c>
       <c r="R15" t="n">
-        <v>6417752</v>
+        <v>6417702</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2172,7 +2173,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>128948462</v>
       </c>
       <c r="B16" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>128948924</v>
       </c>
       <c r="B17" t="n">
-        <v>92273</v>
+        <v>92278</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>128948686</v>
       </c>
       <c r="B18" t="n">
-        <v>92273</v>
+        <v>92278</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>128948597</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>128948980</v>
       </c>
       <c r="B20" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>128948733</v>
       </c>
       <c r="B21" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>128948660</v>
       </c>
       <c r="B22" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>128948844</v>
       </c>
       <c r="B23" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>128948485</v>
       </c>
       <c r="B24" t="n">
-        <v>92273</v>
+        <v>92278</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>128948753</v>
       </c>
       <c r="B25" t="n">
-        <v>57878</v>
+        <v>57881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>128950752</v>
       </c>
       <c r="B26" t="n">
-        <v>91720</v>
+        <v>91725</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>128948452</v>
       </c>
       <c r="B27" t="n">
-        <v>92273</v>
+        <v>92278</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>128949214</v>
       </c>
       <c r="B28" t="n">
-        <v>92308</v>
+        <v>92313</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>128948737</v>
       </c>
       <c r="B29" t="n">
-        <v>92479</v>
+        <v>92484</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -3381,42 +3381,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128949214</v>
+        <v>128948737</v>
       </c>
       <c r="B27" t="n">
-        <v>92321</v>
+        <v>92492</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2014</v>
+        <v>4786</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Kuntze</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3427,13 +3423,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>579338</v>
+        <v>579363</v>
       </c>
       <c r="R27" t="n">
-        <v>6417689</v>
+        <v>6417668</v>
       </c>
       <c r="S27" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3463,11 +3459,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3495,10 +3486,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128948452</v>
+        <v>128949214</v>
       </c>
       <c r="B28" t="n">
-        <v>92286</v>
+        <v>92321</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3506,27 +3497,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>366</v>
+        <v>2014</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3540,10 +3535,10 @@
         <v>579338</v>
       </c>
       <c r="R28" t="n">
-        <v>6417742</v>
+        <v>6417689</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3573,6 +3568,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3600,32 +3600,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128948737</v>
+        <v>128948452</v>
       </c>
       <c r="B29" t="n">
-        <v>92492</v>
+        <v>92286</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4786</v>
+        <v>366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kuntze</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3642,13 +3642,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579363</v>
+        <v>579338</v>
       </c>
       <c r="R29" t="n">
-        <v>6417668</v>
+        <v>6417742</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1980,7 +1980,7 @@
         <v>128948436</v>
       </c>
       <c r="B14" t="n">
-        <v>92286</v>
+        <v>92291</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>128948924</v>
       </c>
       <c r="B17" t="n">
-        <v>92286</v>
+        <v>92291</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>128948686</v>
       </c>
       <c r="B18" t="n">
-        <v>92286</v>
+        <v>92291</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128948753</v>
+        <v>128948485</v>
       </c>
       <c r="B24" t="n">
-        <v>57881</v>
+        <v>92291</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3069,35 +3069,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103020</v>
+        <v>366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3105,13 +3100,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579456</v>
+        <v>579339</v>
       </c>
       <c r="R24" t="n">
-        <v>6417686</v>
+        <v>6417733</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3149,6 +3144,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3167,10 +3163,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128948485</v>
+        <v>128948753</v>
       </c>
       <c r="B25" t="n">
-        <v>92286</v>
+        <v>57881</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3178,30 +3174,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>366</v>
+        <v>103020</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3209,13 +3210,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579339</v>
+        <v>579456</v>
       </c>
       <c r="R25" t="n">
-        <v>6417733</v>
+        <v>6417686</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3253,7 +3254,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>128950752</v>
       </c>
       <c r="B26" t="n">
-        <v>91732</v>
+        <v>91735</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3381,38 +3381,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128948737</v>
+        <v>128949214</v>
       </c>
       <c r="B27" t="n">
-        <v>92492</v>
+        <v>92326</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4786</v>
+        <v>2014</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kuntze</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3423,13 +3427,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>579363</v>
+        <v>579338</v>
       </c>
       <c r="R27" t="n">
-        <v>6417668</v>
+        <v>6417689</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3459,6 +3463,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3486,10 +3495,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128949214</v>
+        <v>128948452</v>
       </c>
       <c r="B28" t="n">
-        <v>92321</v>
+        <v>92291</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3497,31 +3506,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2014</v>
+        <v>366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3535,10 +3540,10 @@
         <v>579338</v>
       </c>
       <c r="R28" t="n">
-        <v>6417689</v>
+        <v>6417742</v>
       </c>
       <c r="S28" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3568,11 +3573,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3600,32 +3600,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128948452</v>
+        <v>128948737</v>
       </c>
       <c r="B29" t="n">
-        <v>92286</v>
+        <v>92497</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>366</v>
+        <v>4786</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.) Kuntze</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3642,13 +3642,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579338</v>
+        <v>579363</v>
       </c>
       <c r="R29" t="n">
-        <v>6417742</v>
+        <v>6417668</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128948436</v>
+        <v>128948895</v>
       </c>
       <c r="B14" t="n">
-        <v>92291</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,44 +1988,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>366</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23022, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579353</v>
+        <v>579414</v>
       </c>
       <c r="R14" t="n">
-        <v>6417752</v>
+        <v>6417702</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2063,7 +2068,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2082,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128948895</v>
+        <v>128948436</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>92294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,49 +2097,44 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 23022, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579414</v>
+        <v>579353</v>
       </c>
       <c r="R15" t="n">
-        <v>6417702</v>
+        <v>6417752</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2173,6 +2172,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>128948924</v>
       </c>
       <c r="B17" t="n">
-        <v>92291</v>
+        <v>92294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>128948686</v>
       </c>
       <c r="B18" t="n">
-        <v>92291</v>
+        <v>92294</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>128948485</v>
       </c>
       <c r="B24" t="n">
-        <v>92291</v>
+        <v>92294</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>128950752</v>
       </c>
       <c r="B26" t="n">
-        <v>91735</v>
+        <v>91738</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3381,10 +3381,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128949214</v>
+        <v>128948452</v>
       </c>
       <c r="B27" t="n">
-        <v>92326</v>
+        <v>92294</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3392,31 +3392,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2014</v>
+        <v>366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3430,10 +3426,10 @@
         <v>579338</v>
       </c>
       <c r="R27" t="n">
-        <v>6417689</v>
+        <v>6417742</v>
       </c>
       <c r="S27" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3463,11 +3459,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3495,10 +3486,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128948452</v>
+        <v>128949214</v>
       </c>
       <c r="B28" t="n">
-        <v>92291</v>
+        <v>92329</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3506,27 +3497,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>366</v>
+        <v>2014</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3540,10 +3535,10 @@
         <v>579338</v>
       </c>
       <c r="R28" t="n">
-        <v>6417742</v>
+        <v>6417689</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3573,6 +3568,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,7 +3603,7 @@
         <v>128948737</v>
       </c>
       <c r="B29" t="n">
-        <v>92497</v>
+        <v>92500</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128948895</v>
+        <v>128948436</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>92294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,49 +1988,44 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 23022, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579414</v>
+        <v>579353</v>
       </c>
       <c r="R14" t="n">
-        <v>6417702</v>
+        <v>6417752</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2068,6 +2063,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128948436</v>
+        <v>128948895</v>
       </c>
       <c r="B15" t="n">
-        <v>92294</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,44 +2093,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>366</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23022, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579353</v>
+        <v>579414</v>
       </c>
       <c r="R15" t="n">
-        <v>6417752</v>
+        <v>6417702</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2172,7 +2173,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -3486,42 +3486,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128949214</v>
+        <v>128948737</v>
       </c>
       <c r="B28" t="n">
-        <v>92329</v>
+        <v>92500</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2014</v>
+        <v>4786</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Kuntze</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3532,13 +3528,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579338</v>
+        <v>579363</v>
       </c>
       <c r="R28" t="n">
-        <v>6417689</v>
+        <v>6417668</v>
       </c>
       <c r="S28" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3568,11 +3564,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3600,38 +3591,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128948737</v>
+        <v>128949214</v>
       </c>
       <c r="B29" t="n">
-        <v>92500</v>
+        <v>92329</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4786</v>
+        <v>2014</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kuntze</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -3642,13 +3637,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579363</v>
+        <v>579338</v>
       </c>
       <c r="R29" t="n">
-        <v>6417668</v>
+        <v>6417689</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3678,6 +3673,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128948436</v>
+        <v>128948895</v>
       </c>
       <c r="B14" t="n">
-        <v>92294</v>
+        <v>57720</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,44 +1988,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>366</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23022, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579353</v>
+        <v>579414</v>
       </c>
       <c r="R14" t="n">
-        <v>6417752</v>
+        <v>6417702</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2063,7 +2068,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2082,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128948895</v>
+        <v>128948436</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>92294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,49 +2097,44 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 23022, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579414</v>
+        <v>579353</v>
       </c>
       <c r="R15" t="n">
-        <v>6417702</v>
+        <v>6417752</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2173,6 +2172,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2844,7 +2844,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128948660</v>
+        <v>128948844</v>
       </c>
       <c r="B22" t="n">
         <v>57720</v>
@@ -2872,28 +2872,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23022, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579336</v>
+        <v>579382</v>
       </c>
       <c r="R22" t="n">
-        <v>6417683</v>
+        <v>6417694</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2949,7 +2953,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128948844</v>
+        <v>128948660</v>
       </c>
       <c r="B23" t="n">
         <v>57720</v>
@@ -2977,32 +2981,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 23022, Häckenstad, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>579382</v>
+        <v>579336</v>
       </c>
       <c r="R23" t="n">
-        <v>6417694</v>
+        <v>6417683</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128948485</v>
+        <v>128948753</v>
       </c>
       <c r="B24" t="n">
-        <v>92294</v>
+        <v>57881</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3069,30 +3069,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>366</v>
+        <v>103020</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3100,13 +3105,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579339</v>
+        <v>579456</v>
       </c>
       <c r="R24" t="n">
-        <v>6417733</v>
+        <v>6417686</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3144,7 +3149,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3163,10 +3167,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128948753</v>
+        <v>128948485</v>
       </c>
       <c r="B25" t="n">
-        <v>57881</v>
+        <v>92294</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3174,35 +3178,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103020</v>
+        <v>366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3210,13 +3209,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579456</v>
+        <v>579339</v>
       </c>
       <c r="R25" t="n">
-        <v>6417686</v>
+        <v>6417733</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3254,6 +3253,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3381,10 +3381,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128948452</v>
+        <v>128949214</v>
       </c>
       <c r="B27" t="n">
-        <v>92294</v>
+        <v>92329</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3392,27 +3392,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>366</v>
+        <v>2014</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3426,10 +3430,10 @@
         <v>579338</v>
       </c>
       <c r="R27" t="n">
-        <v>6417742</v>
+        <v>6417689</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3459,6 +3463,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,10 +3600,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128949214</v>
+        <v>128948452</v>
       </c>
       <c r="B29" t="n">
-        <v>92329</v>
+        <v>92294</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3602,31 +3611,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2014</v>
+        <v>366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -3640,10 +3645,10 @@
         <v>579338</v>
       </c>
       <c r="R29" t="n">
-        <v>6417689</v>
+        <v>6417742</v>
       </c>
       <c r="S29" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3673,11 +3678,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1980,7 +1980,7 @@
         <v>128948895</v>
       </c>
       <c r="B14" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>128948436</v>
       </c>
       <c r="B15" t="n">
-        <v>92294</v>
+        <v>92301</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>128948462</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>128948924</v>
       </c>
       <c r="B17" t="n">
-        <v>92294</v>
+        <v>92301</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>128948686</v>
       </c>
       <c r="B18" t="n">
-        <v>92294</v>
+        <v>92301</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>128948597</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57738</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>128948980</v>
       </c>
       <c r="B20" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>128948733</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128948844</v>
+        <v>128948660</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,32 +2872,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 23022, Häckenstad, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579382</v>
+        <v>579336</v>
       </c>
       <c r="R22" t="n">
-        <v>6417694</v>
+        <v>6417683</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2953,10 +2949,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128948660</v>
+        <v>128948844</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2981,28 +2977,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23022, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>579336</v>
+        <v>579382</v>
       </c>
       <c r="R23" t="n">
-        <v>6417683</v>
+        <v>6417694</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>128948753</v>
       </c>
       <c r="B24" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>128948485</v>
       </c>
       <c r="B25" t="n">
-        <v>92294</v>
+        <v>92301</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>128950752</v>
       </c>
       <c r="B26" t="n">
-        <v>91738</v>
+        <v>91745</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>128949214</v>
       </c>
       <c r="B27" t="n">
-        <v>92329</v>
+        <v>92336</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3495,32 +3495,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128948737</v>
+        <v>128948452</v>
       </c>
       <c r="B28" t="n">
-        <v>92500</v>
+        <v>92301</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4786</v>
+        <v>366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kuntze</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3537,13 +3537,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579363</v>
+        <v>579338</v>
       </c>
       <c r="R28" t="n">
-        <v>6417668</v>
+        <v>6417742</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3600,32 +3600,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128948452</v>
+        <v>128948737</v>
       </c>
       <c r="B29" t="n">
-        <v>92294</v>
+        <v>92507</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>366</v>
+        <v>4786</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.) Kuntze</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3642,13 +3642,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579338</v>
+        <v>579363</v>
       </c>
       <c r="R29" t="n">
-        <v>6417742</v>
+        <v>6417668</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128948895</v>
+        <v>128948436</v>
       </c>
       <c r="B14" t="n">
-        <v>57722</v>
+        <v>92308</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,49 +1988,44 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 23022, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579414</v>
+        <v>579353</v>
       </c>
       <c r="R14" t="n">
-        <v>6417702</v>
+        <v>6417752</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2068,6 +2063,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128948436</v>
+        <v>128948895</v>
       </c>
       <c r="B15" t="n">
-        <v>92301</v>
+        <v>57722</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,44 +2093,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>366</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23022, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579353</v>
+        <v>579414</v>
       </c>
       <c r="R15" t="n">
-        <v>6417752</v>
+        <v>6417702</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2172,7 +2173,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128948924</v>
+        <v>128948686</v>
       </c>
       <c r="B17" t="n">
-        <v>92301</v>
+        <v>92308</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579284</v>
+        <v>579336</v>
       </c>
       <c r="R17" t="n">
-        <v>6417717</v>
+        <v>6417683</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128948686</v>
+        <v>128948924</v>
       </c>
       <c r="B18" t="n">
-        <v>92301</v>
+        <v>92308</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579336</v>
+        <v>579284</v>
       </c>
       <c r="R18" t="n">
-        <v>6417683</v>
+        <v>6417717</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3058,10 +3058,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128948753</v>
+        <v>128948485</v>
       </c>
       <c r="B24" t="n">
-        <v>57883</v>
+        <v>92308</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3069,35 +3069,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103020</v>
+        <v>366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3105,13 +3100,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579456</v>
+        <v>579339</v>
       </c>
       <c r="R24" t="n">
-        <v>6417686</v>
+        <v>6417733</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3149,6 +3144,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3167,10 +3163,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128948485</v>
+        <v>128948753</v>
       </c>
       <c r="B25" t="n">
-        <v>92301</v>
+        <v>57883</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3178,30 +3174,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>366</v>
+        <v>103020</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3209,13 +3210,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579339</v>
+        <v>579456</v>
       </c>
       <c r="R25" t="n">
-        <v>6417733</v>
+        <v>6417686</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3253,7 +3254,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>128950752</v>
       </c>
       <c r="B26" t="n">
-        <v>91745</v>
+        <v>91752</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3381,10 +3381,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128949214</v>
+        <v>128948452</v>
       </c>
       <c r="B27" t="n">
-        <v>92336</v>
+        <v>92308</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3392,31 +3392,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2014</v>
+        <v>366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3430,10 +3426,10 @@
         <v>579338</v>
       </c>
       <c r="R27" t="n">
-        <v>6417689</v>
+        <v>6417742</v>
       </c>
       <c r="S27" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3463,11 +3459,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3495,10 +3486,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128948452</v>
+        <v>128949214</v>
       </c>
       <c r="B28" t="n">
-        <v>92301</v>
+        <v>92343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3506,27 +3497,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>366</v>
+        <v>2014</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3540,10 +3535,10 @@
         <v>579338</v>
       </c>
       <c r="R28" t="n">
-        <v>6417742</v>
+        <v>6417689</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3573,6 +3568,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3603,7 +3603,7 @@
         <v>128948737</v>
       </c>
       <c r="B29" t="n">
-        <v>92507</v>
+        <v>92514</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1980,7 +1980,7 @@
         <v>128948436</v>
       </c>
       <c r="B14" t="n">
-        <v>92308</v>
+        <v>92310</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>128948895</v>
       </c>
       <c r="B15" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>128948462</v>
       </c>
       <c r="B16" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128948686</v>
+        <v>128948924</v>
       </c>
       <c r="B17" t="n">
-        <v>92308</v>
+        <v>92310</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,10 +2343,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579336</v>
+        <v>579284</v>
       </c>
       <c r="R17" t="n">
-        <v>6417683</v>
+        <v>6417717</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128948924</v>
+        <v>128948686</v>
       </c>
       <c r="B18" t="n">
-        <v>92308</v>
+        <v>92310</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579284</v>
+        <v>579336</v>
       </c>
       <c r="R18" t="n">
-        <v>6417717</v>
+        <v>6417683</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2514,7 +2514,7 @@
         <v>128948597</v>
       </c>
       <c r="B19" t="n">
-        <v>57738</v>
+        <v>57740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>128948980</v>
       </c>
       <c r="B20" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>128948733</v>
       </c>
       <c r="B21" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>128948660</v>
       </c>
       <c r="B22" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>128948844</v>
       </c>
       <c r="B23" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>128948485</v>
       </c>
       <c r="B24" t="n">
-        <v>92308</v>
+        <v>92310</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>128948753</v>
       </c>
       <c r="B25" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>128950752</v>
       </c>
       <c r="B26" t="n">
-        <v>91752</v>
+        <v>91754</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3381,10 +3381,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128948452</v>
+        <v>128949214</v>
       </c>
       <c r="B27" t="n">
-        <v>92308</v>
+        <v>92345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3392,27 +3392,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>366</v>
+        <v>2014</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3426,10 +3430,10 @@
         <v>579338</v>
       </c>
       <c r="R27" t="n">
-        <v>6417742</v>
+        <v>6417689</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3459,6 +3463,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3486,42 +3495,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128949214</v>
+        <v>128948737</v>
       </c>
       <c r="B28" t="n">
-        <v>92343</v>
+        <v>92516</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2014</v>
+        <v>4786</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Kuntze</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3532,13 +3537,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579338</v>
+        <v>579363</v>
       </c>
       <c r="R28" t="n">
-        <v>6417689</v>
+        <v>6417668</v>
       </c>
       <c r="S28" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3568,11 +3573,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3600,32 +3600,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128948737</v>
+        <v>128948452</v>
       </c>
       <c r="B29" t="n">
-        <v>92514</v>
+        <v>92310</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4786</v>
+        <v>366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kuntze</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3642,13 +3642,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579363</v>
+        <v>579338</v>
       </c>
       <c r="R29" t="n">
-        <v>6417668</v>
+        <v>6417742</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -3381,10 +3381,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128949214</v>
+        <v>128948452</v>
       </c>
       <c r="B27" t="n">
-        <v>92345</v>
+        <v>92310</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3392,31 +3392,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2014</v>
+        <v>366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3430,10 +3426,10 @@
         <v>579338</v>
       </c>
       <c r="R27" t="n">
-        <v>6417689</v>
+        <v>6417742</v>
       </c>
       <c r="S27" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3463,11 +3459,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3495,38 +3486,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128948737</v>
+        <v>128949214</v>
       </c>
       <c r="B28" t="n">
-        <v>92516</v>
+        <v>92345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4786</v>
+        <v>2014</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kuntze</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3537,13 +3532,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579363</v>
+        <v>579338</v>
       </c>
       <c r="R28" t="n">
-        <v>6417668</v>
+        <v>6417689</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3573,6 +3568,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3600,32 +3600,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128948452</v>
+        <v>128948737</v>
       </c>
       <c r="B29" t="n">
-        <v>92310</v>
+        <v>92516</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>366</v>
+        <v>4786</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.) Kuntze</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3642,13 +3642,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579338</v>
+        <v>579363</v>
       </c>
       <c r="R29" t="n">
-        <v>6417742</v>
+        <v>6417668</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -3486,42 +3486,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128949214</v>
+        <v>128948737</v>
       </c>
       <c r="B28" t="n">
-        <v>92345</v>
+        <v>92516</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2014</v>
+        <v>4786</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Kuntze</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3532,13 +3528,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579338</v>
+        <v>579363</v>
       </c>
       <c r="R28" t="n">
-        <v>6417689</v>
+        <v>6417668</v>
       </c>
       <c r="S28" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3568,11 +3564,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3600,38 +3591,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128948737</v>
+        <v>128949214</v>
       </c>
       <c r="B29" t="n">
-        <v>92516</v>
+        <v>92345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4786</v>
+        <v>2014</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kuntze</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -3642,13 +3637,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579363</v>
+        <v>579338</v>
       </c>
       <c r="R29" t="n">
-        <v>6417668</v>
+        <v>6417689</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3678,6 +3673,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1980,7 +1980,7 @@
         <v>128948436</v>
       </c>
       <c r="B14" t="n">
-        <v>92310</v>
+        <v>92324</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>128948924</v>
       </c>
       <c r="B17" t="n">
-        <v>92310</v>
+        <v>92324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>128948686</v>
       </c>
       <c r="B18" t="n">
-        <v>92310</v>
+        <v>92324</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>128948485</v>
       </c>
       <c r="B24" t="n">
-        <v>92310</v>
+        <v>92324</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>128950752</v>
       </c>
       <c r="B26" t="n">
-        <v>91754</v>
+        <v>91763</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3381,32 +3381,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128948452</v>
+        <v>128948737</v>
       </c>
       <c r="B27" t="n">
-        <v>92310</v>
+        <v>92530</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>366</v>
+        <v>4786</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.) Kuntze</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3423,13 +3423,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>579338</v>
+        <v>579363</v>
       </c>
       <c r="R27" t="n">
-        <v>6417742</v>
+        <v>6417668</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3486,32 +3486,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128948737</v>
+        <v>128948452</v>
       </c>
       <c r="B28" t="n">
-        <v>92516</v>
+        <v>92324</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4786</v>
+        <v>366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kuntze</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3528,13 +3528,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579363</v>
+        <v>579338</v>
       </c>
       <c r="R28" t="n">
-        <v>6417668</v>
+        <v>6417742</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>128949214</v>
       </c>
       <c r="B29" t="n">
-        <v>92345</v>
+        <v>92359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128948436</v>
+        <v>128948895</v>
       </c>
       <c r="B14" t="n">
-        <v>92324</v>
+        <v>57724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,44 +1988,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>366</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23022, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579353</v>
+        <v>579414</v>
       </c>
       <c r="R14" t="n">
-        <v>6417752</v>
+        <v>6417702</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2063,7 +2068,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2082,10 +2086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128948895</v>
+        <v>128948436</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>92325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,49 +2097,44 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 23022, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579414</v>
+        <v>579353</v>
       </c>
       <c r="R15" t="n">
-        <v>6417702</v>
+        <v>6417752</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2173,6 +2172,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>128948924</v>
       </c>
       <c r="B17" t="n">
-        <v>92324</v>
+        <v>92325</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>128948686</v>
       </c>
       <c r="B18" t="n">
-        <v>92324</v>
+        <v>92325</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>128948485</v>
       </c>
       <c r="B24" t="n">
-        <v>92324</v>
+        <v>92325</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>128950752</v>
       </c>
       <c r="B26" t="n">
-        <v>91763</v>
+        <v>91764</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>128948737</v>
       </c>
       <c r="B27" t="n">
-        <v>92530</v>
+        <v>92531</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3486,10 +3486,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128948452</v>
+        <v>128949214</v>
       </c>
       <c r="B28" t="n">
-        <v>92324</v>
+        <v>92360</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3497,27 +3497,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>366</v>
+        <v>2014</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3531,10 +3535,10 @@
         <v>579338</v>
       </c>
       <c r="R28" t="n">
-        <v>6417742</v>
+        <v>6417689</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3564,6 +3568,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3591,10 +3600,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128949214</v>
+        <v>128948452</v>
       </c>
       <c r="B29" t="n">
-        <v>92359</v>
+        <v>92325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3602,31 +3611,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2014</v>
+        <v>366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -3640,10 +3645,10 @@
         <v>579338</v>
       </c>
       <c r="R29" t="n">
-        <v>6417689</v>
+        <v>6417742</v>
       </c>
       <c r="S29" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3673,11 +3678,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128948895</v>
+        <v>128948436</v>
       </c>
       <c r="B14" t="n">
-        <v>57724</v>
+        <v>92325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,49 +1988,44 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 23022, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579414</v>
+        <v>579353</v>
       </c>
       <c r="R14" t="n">
-        <v>6417702</v>
+        <v>6417752</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2068,6 +2063,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2086,10 +2082,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128948436</v>
+        <v>128948895</v>
       </c>
       <c r="B15" t="n">
-        <v>92325</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,44 +2093,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>366</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23022, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579353</v>
+        <v>579414</v>
       </c>
       <c r="R15" t="n">
-        <v>6417752</v>
+        <v>6417702</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2172,7 +2173,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -3381,38 +3381,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128948737</v>
+        <v>128949214</v>
       </c>
       <c r="B27" t="n">
-        <v>92531</v>
+        <v>92360</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4786</v>
+        <v>2014</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kuntze</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3423,13 +3427,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>579363</v>
+        <v>579338</v>
       </c>
       <c r="R27" t="n">
-        <v>6417668</v>
+        <v>6417689</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3459,6 +3463,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3486,10 +3495,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128949214</v>
+        <v>128948452</v>
       </c>
       <c r="B28" t="n">
-        <v>92360</v>
+        <v>92325</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3497,31 +3506,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2014</v>
+        <v>366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3535,10 +3540,10 @@
         <v>579338</v>
       </c>
       <c r="R28" t="n">
-        <v>6417689</v>
+        <v>6417742</v>
       </c>
       <c r="S28" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3568,11 +3573,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3600,32 +3600,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128948452</v>
+        <v>128948737</v>
       </c>
       <c r="B29" t="n">
-        <v>92325</v>
+        <v>92531</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>366</v>
+        <v>4786</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.) Kuntze</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3642,13 +3642,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579338</v>
+        <v>579363</v>
       </c>
       <c r="R29" t="n">
-        <v>6417742</v>
+        <v>6417668</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1980,7 +1980,7 @@
         <v>128948436</v>
       </c>
       <c r="B14" t="n">
-        <v>92325</v>
+        <v>92328</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>128948924</v>
       </c>
       <c r="B17" t="n">
-        <v>92325</v>
+        <v>92328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>128948686</v>
       </c>
       <c r="B18" t="n">
-        <v>92325</v>
+        <v>92328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128948485</v>
+        <v>128948753</v>
       </c>
       <c r="B24" t="n">
-        <v>92325</v>
+        <v>57885</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3069,30 +3069,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>366</v>
+        <v>103020</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3100,13 +3105,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579339</v>
+        <v>579456</v>
       </c>
       <c r="R24" t="n">
-        <v>6417733</v>
+        <v>6417686</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3144,7 +3149,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3163,10 +3167,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128948753</v>
+        <v>128948485</v>
       </c>
       <c r="B25" t="n">
-        <v>57885</v>
+        <v>92328</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3174,35 +3178,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103020</v>
+        <v>366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3210,13 +3209,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579456</v>
+        <v>579339</v>
       </c>
       <c r="R25" t="n">
-        <v>6417686</v>
+        <v>6417733</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3254,6 +3253,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>128950752</v>
       </c>
       <c r="B26" t="n">
-        <v>91764</v>
+        <v>91767</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>128949214</v>
       </c>
       <c r="B27" t="n">
-        <v>92360</v>
+        <v>92363</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>128948452</v>
       </c>
       <c r="B28" t="n">
-        <v>92325</v>
+        <v>92328</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>128948737</v>
       </c>
       <c r="B29" t="n">
-        <v>92531</v>
+        <v>92534</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1980,7 +1980,7 @@
         <v>128948436</v>
       </c>
       <c r="B14" t="n">
-        <v>92328</v>
+        <v>92330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>128948924</v>
       </c>
       <c r="B17" t="n">
-        <v>92328</v>
+        <v>92330</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>128948686</v>
       </c>
       <c r="B18" t="n">
-        <v>92328</v>
+        <v>92330</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128948753</v>
+        <v>128948485</v>
       </c>
       <c r="B24" t="n">
-        <v>57885</v>
+        <v>92330</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3069,35 +3069,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103020</v>
+        <v>366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3105,13 +3100,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579456</v>
+        <v>579339</v>
       </c>
       <c r="R24" t="n">
-        <v>6417686</v>
+        <v>6417733</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3149,6 +3144,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3167,10 +3163,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128948485</v>
+        <v>128948753</v>
       </c>
       <c r="B25" t="n">
-        <v>92328</v>
+        <v>57885</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3178,30 +3174,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>366</v>
+        <v>103020</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3209,13 +3210,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579339</v>
+        <v>579456</v>
       </c>
       <c r="R25" t="n">
-        <v>6417733</v>
+        <v>6417686</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3253,7 +3254,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>128950752</v>
       </c>
       <c r="B26" t="n">
-        <v>91767</v>
+        <v>91769</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>128949214</v>
       </c>
       <c r="B27" t="n">
-        <v>92363</v>
+        <v>92365</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3495,32 +3495,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128948452</v>
+        <v>128948737</v>
       </c>
       <c r="B28" t="n">
-        <v>92328</v>
+        <v>92536</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>366</v>
+        <v>4786</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.) Kuntze</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3537,13 +3537,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579338</v>
+        <v>579363</v>
       </c>
       <c r="R28" t="n">
-        <v>6417742</v>
+        <v>6417668</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3600,32 +3600,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128948737</v>
+        <v>128948452</v>
       </c>
       <c r="B29" t="n">
-        <v>92534</v>
+        <v>92330</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4786</v>
+        <v>366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kuntze</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3642,13 +3642,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579363</v>
+        <v>579338</v>
       </c>
       <c r="R29" t="n">
-        <v>6417668</v>
+        <v>6417742</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1980,7 +1980,7 @@
         <v>128948436</v>
       </c>
       <c r="B14" t="n">
-        <v>92330</v>
+        <v>92334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>128948924</v>
       </c>
       <c r="B17" t="n">
-        <v>92330</v>
+        <v>92334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>128948686</v>
       </c>
       <c r="B18" t="n">
-        <v>92330</v>
+        <v>92334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128948485</v>
+        <v>128948753</v>
       </c>
       <c r="B24" t="n">
-        <v>92330</v>
+        <v>57885</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3069,30 +3069,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>366</v>
+        <v>103020</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3100,13 +3105,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579339</v>
+        <v>579456</v>
       </c>
       <c r="R24" t="n">
-        <v>6417733</v>
+        <v>6417686</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3144,7 +3149,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3163,10 +3167,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128948753</v>
+        <v>128948485</v>
       </c>
       <c r="B25" t="n">
-        <v>57885</v>
+        <v>92334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3174,35 +3178,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103020</v>
+        <v>366</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3210,13 +3209,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579456</v>
+        <v>579339</v>
       </c>
       <c r="R25" t="n">
-        <v>6417686</v>
+        <v>6417733</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3254,6 +3253,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>128950752</v>
       </c>
       <c r="B26" t="n">
-        <v>91769</v>
+        <v>91773</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3381,10 +3381,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128949214</v>
+        <v>128948452</v>
       </c>
       <c r="B27" t="n">
-        <v>92365</v>
+        <v>92334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3392,31 +3392,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2014</v>
+        <v>366</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3430,10 +3426,10 @@
         <v>579338</v>
       </c>
       <c r="R27" t="n">
-        <v>6417689</v>
+        <v>6417742</v>
       </c>
       <c r="S27" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3463,11 +3459,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3495,38 +3486,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128948737</v>
+        <v>128949214</v>
       </c>
       <c r="B28" t="n">
-        <v>92536</v>
+        <v>92369</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4786</v>
+        <v>2014</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kuntze</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3537,13 +3532,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579363</v>
+        <v>579338</v>
       </c>
       <c r="R28" t="n">
-        <v>6417668</v>
+        <v>6417689</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3573,6 +3568,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3600,32 +3600,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128948452</v>
+        <v>128948737</v>
       </c>
       <c r="B29" t="n">
-        <v>92330</v>
+        <v>92540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>366</v>
+        <v>4786</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.) Kuntze</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3642,13 +3642,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579338</v>
+        <v>579363</v>
       </c>
       <c r="R29" t="n">
-        <v>6417742</v>
+        <v>6417668</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -1980,7 +1980,7 @@
         <v>128948436</v>
       </c>
       <c r="B14" t="n">
-        <v>92334</v>
+        <v>92335</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>128948924</v>
       </c>
       <c r="B17" t="n">
-        <v>92334</v>
+        <v>92335</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>128948686</v>
       </c>
       <c r="B18" t="n">
-        <v>92334</v>
+        <v>92335</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128948753</v>
+        <v>128948485</v>
       </c>
       <c r="B24" t="n">
-        <v>57885</v>
+        <v>92335</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3069,35 +3069,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103020</v>
+        <v>366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3105,13 +3100,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579456</v>
+        <v>579339</v>
       </c>
       <c r="R24" t="n">
-        <v>6417686</v>
+        <v>6417733</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3149,6 +3144,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3167,10 +3163,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128948485</v>
+        <v>128948753</v>
       </c>
       <c r="B25" t="n">
-        <v>92334</v>
+        <v>57885</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3178,30 +3174,35 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>366</v>
+        <v>103020</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3209,13 +3210,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579339</v>
+        <v>579456</v>
       </c>
       <c r="R25" t="n">
-        <v>6417733</v>
+        <v>6417686</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3253,7 +3254,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>128950752</v>
       </c>
       <c r="B26" t="n">
-        <v>91773</v>
+        <v>91774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3381,32 +3381,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128948452</v>
+        <v>128948737</v>
       </c>
       <c r="B27" t="n">
-        <v>92334</v>
+        <v>92541</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>366</v>
+        <v>4786</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.) Kuntze</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3423,13 +3423,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>579338</v>
+        <v>579363</v>
       </c>
       <c r="R27" t="n">
-        <v>6417742</v>
+        <v>6417668</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>128949214</v>
       </c>
       <c r="B28" t="n">
-        <v>92369</v>
+        <v>92370</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3600,32 +3600,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128948737</v>
+        <v>128948452</v>
       </c>
       <c r="B29" t="n">
-        <v>92540</v>
+        <v>92335</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4786</v>
+        <v>366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kuntze</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3642,13 +3642,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579363</v>
+        <v>579338</v>
       </c>
       <c r="R29" t="n">
-        <v>6417668</v>
+        <v>6417742</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -3579,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -2514,7 +2514,7 @@
         <v>128948597</v>
       </c>
       <c r="B19" t="n">
-        <v>57897</v>
+        <v>57740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 23021-2025 artfynd.xlsx
+++ b/artfynd/A 23021-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125110121</v>
+        <v>128948436</v>
       </c>
       <c r="B2" t="n">
-        <v>57932</v>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,35 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579349</v>
+        <v>579353</v>
       </c>
       <c r="R2" t="n">
-        <v>6417761</v>
+        <v>6417752</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,12 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +761,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125110523</v>
+        <v>128948452</v>
       </c>
       <c r="B3" t="n">
-        <v>91240</v>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,28 +791,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -830,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579507</v>
+        <v>579338</v>
       </c>
       <c r="R3" t="n">
-        <v>6417672</v>
+        <v>6417742</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,42 +885,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125110359</v>
+        <v>128948485</v>
       </c>
       <c r="B4" t="n">
-        <v>58044</v>
+        <v>92699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,13 +927,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579299</v>
+        <v>579339</v>
       </c>
       <c r="R4" t="n">
-        <v>6417671</v>
+        <v>6417733</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,6 +971,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -998,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125110184</v>
+        <v>128948686</v>
       </c>
       <c r="B5" t="n">
-        <v>57932</v>
+        <v>92699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,35 +1001,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,13 +1032,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579324</v>
+        <v>579336</v>
       </c>
       <c r="R5" t="n">
-        <v>6417713</v>
+        <v>6417683</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1075,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,6 +1076,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1107,42 +1095,41 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125110671</v>
+        <v>128948924</v>
       </c>
       <c r="B6" t="n">
-        <v>58044</v>
+        <v>92699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103037</v>
+        <v>366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1150,13 +1137,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579247</v>
+        <v>579284</v>
       </c>
       <c r="R6" t="n">
-        <v>6417660</v>
+        <v>6417717</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1180,12 +1167,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,6 +1181,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1212,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125110297</v>
+        <v>125110444</v>
       </c>
       <c r="B7" t="n">
-        <v>91240</v>
+        <v>90946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1223,31 +1211,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>889</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1258,13 +1246,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579324</v>
+        <v>579436</v>
       </c>
       <c r="R7" t="n">
-        <v>6417713</v>
+        <v>6417634</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1294,6 +1282,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mkt gammal tall på berget.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125110326</v>
+        <v>128950752</v>
       </c>
       <c r="B8" t="n">
-        <v>91240</v>
+        <v>92134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,31 +1325,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>1106</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1367,13 +1360,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579314</v>
+        <v>579338</v>
       </c>
       <c r="R8" t="n">
         <v>6417689</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,12 +1390,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125110571</v>
+        <v>128949214</v>
       </c>
       <c r="B9" t="n">
-        <v>57648</v>
+        <v>92732</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1441,35 +1434,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2014</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1477,13 +1469,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579507</v>
+        <v>579338</v>
       </c>
       <c r="R9" t="n">
-        <v>6417672</v>
+        <v>6417689</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,20 +1499,26 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1539,42 +1537,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125110444</v>
+        <v>128948737</v>
       </c>
       <c r="B10" t="n">
-        <v>90270</v>
+        <v>92905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>889</v>
+        <v>4786</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Irpicodon pendulus</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kuntze</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1585,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579436</v>
+        <v>579363</v>
       </c>
       <c r="R10" t="n">
-        <v>6417634</v>
+        <v>6417668</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1615,17 +1609,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mkt gammal tall på berget.</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1642,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125110495</v>
+        <v>125110297</v>
       </c>
       <c r="B11" t="n">
-        <v>57664</v>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,31 +1653,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100048</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1696,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579536</v>
+        <v>579324</v>
       </c>
       <c r="R11" t="n">
-        <v>6417623</v>
+        <v>6417713</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,17 +1726,13 @@
           <t>2025-05-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Nu bebott av nötväcka!</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1763,56 +1751,59 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125110142</v>
+        <v>125110326</v>
       </c>
       <c r="B12" t="n">
-        <v>58044</v>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103037</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>bo, hörda ungar</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 23021, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579356</v>
+        <v>579314</v>
       </c>
       <c r="R12" t="n">
-        <v>6417758</v>
+        <v>6417689</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1850,6 +1841,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1868,32 +1860,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125110180</v>
+        <v>125110523</v>
       </c>
       <c r="B13" t="n">
-        <v>56947</v>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100038</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1901,13 +1893,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1915,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579324</v>
+        <v>579507</v>
       </c>
       <c r="R13" t="n">
-        <v>6417713</v>
+        <v>6417672</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1959,6 +1950,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1977,41 +1969,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128948436</v>
+        <v>125110180</v>
       </c>
       <c r="B14" t="n">
-        <v>92335</v>
+        <v>57247</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>366</v>
+        <v>100038</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2019,13 +2016,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579353</v>
+        <v>579324</v>
       </c>
       <c r="R14" t="n">
-        <v>6417752</v>
+        <v>6417713</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2049,12 +2046,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,7 +2060,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2082,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128948895</v>
+        <v>125110495</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>57966</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,16 +2089,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2110,32 +2106,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>A 23022, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579414</v>
+        <v>579536</v>
       </c>
       <c r="R15" t="n">
-        <v>6417702</v>
+        <v>6417623</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2159,12 +2151,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Nu bebott av nötväcka!</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128948462</v>
+        <v>128948597</v>
       </c>
       <c r="B16" t="n">
-        <v>57724</v>
+        <v>57966</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2202,16 +2199,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2219,12 +2216,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2234,13 +2235,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579338</v>
+        <v>579324</v>
       </c>
       <c r="R16" t="n">
-        <v>6417742</v>
+        <v>6417730</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2274,7 +2275,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Födosöksspår</t>
+          <t>Svarade på uppspelning.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2301,41 +2302,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128948924</v>
+        <v>125110571</v>
       </c>
       <c r="B17" t="n">
-        <v>92335</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>366</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2343,13 +2349,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579284</v>
+        <v>579507</v>
       </c>
       <c r="R17" t="n">
-        <v>6417717</v>
+        <v>6417672</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2373,12 +2379,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2393,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2406,41 +2411,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128948686</v>
+        <v>128948462</v>
       </c>
       <c r="B18" t="n">
-        <v>92335</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>366</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2448,10 +2454,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579336</v>
+        <v>579338</v>
       </c>
       <c r="R18" t="n">
-        <v>6417683</v>
+        <v>6417742</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2486,13 +2492,17 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födosöksspår</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2511,27 +2521,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128948597</v>
+        <v>128948660</v>
       </c>
       <c r="B19" t="n">
-        <v>57740</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2539,16 +2549,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2558,13 +2564,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579324</v>
+        <v>579336</v>
       </c>
       <c r="R19" t="n">
-        <v>6417730</v>
+        <v>6417683</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2594,11 +2600,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Svarade på uppspelning.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2625,14 +2626,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128948980</v>
+        <v>128948733</v>
       </c>
       <c r="B20" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2653,12 +2654,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2668,13 +2673,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579267</v>
+        <v>579363</v>
       </c>
       <c r="R20" t="n">
-        <v>6417704</v>
+        <v>6417668</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2704,11 +2709,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bearbetat torrträd</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2735,14 +2735,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128948733</v>
+        <v>128948844</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2778,14 +2778,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23022, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>579363</v>
+        <v>579382</v>
       </c>
       <c r="R21" t="n">
-        <v>6417668</v>
+        <v>6417694</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2844,14 +2844,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128948660</v>
+        <v>128948895</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2872,28 +2872,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23022, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579336</v>
+        <v>579414</v>
       </c>
       <c r="R22" t="n">
-        <v>6417683</v>
+        <v>6417702</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2949,14 +2953,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128948844</v>
+        <v>128948980</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2977,32 +2981,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>A 23022, Häckenstad, Sm</t>
+          <t>A 23021, Häckenstad, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>579382</v>
+        <v>579267</v>
       </c>
       <c r="R23" t="n">
-        <v>6417694</v>
+        <v>6417704</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3032,6 +3032,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Bearbetat torrträd</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3058,10 +3063,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128948485</v>
+        <v>125110121</v>
       </c>
       <c r="B24" t="n">
-        <v>92335</v>
+        <v>58238</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3069,30 +3074,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>366</v>
+        <v>103012</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3100,13 +3110,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579339</v>
+        <v>579349</v>
       </c>
       <c r="R24" t="n">
-        <v>6417733</v>
+        <v>6417761</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3130,12 +3140,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3144,7 +3154,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3163,10 +3172,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128948753</v>
+        <v>125110184</v>
       </c>
       <c r="B25" t="n">
-        <v>57885</v>
+        <v>58238</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3174,21 +3183,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103020</v>
+        <v>103012</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3200,7 +3209,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3210,10 +3219,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579456</v>
+        <v>579324</v>
       </c>
       <c r="R25" t="n">
-        <v>6417686</v>
+        <v>6417713</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3240,12 +3249,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3272,32 +3281,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128950752</v>
+        <v>128948753</v>
       </c>
       <c r="B26" t="n">
-        <v>91774</v>
+        <v>58112</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1106</v>
+        <v>103020</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3305,12 +3314,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3318,13 +3328,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>579338</v>
+        <v>579456</v>
       </c>
       <c r="R26" t="n">
-        <v>6417689</v>
+        <v>6417686</v>
       </c>
       <c r="S26" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3362,7 +3372,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3381,52 +3390,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128948737</v>
+        <v>125110142</v>
       </c>
       <c r="B27" t="n">
-        <v>92541</v>
+        <v>58353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4786</v>
+        <v>103037</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactifluus volemus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kuntze</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>A 23021, Häckenstad, Sm</t>
+          <t>A 23021, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>579363</v>
+        <v>579356</v>
       </c>
       <c r="R27" t="n">
-        <v>6417668</v>
+        <v>6417758</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3453,12 +3463,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3467,7 +3477,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3486,45 +3495,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128949214</v>
+        <v>125110359</v>
       </c>
       <c r="B28" t="n">
-        <v>92370</v>
+        <v>58353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2014</v>
+        <v>103037</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3532,13 +3538,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579338</v>
+        <v>579299</v>
       </c>
       <c r="R28" t="n">
-        <v>6417689</v>
+        <v>6417671</v>
       </c>
       <c r="S28" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3562,26 +3568,20 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På två olika substrat, men i mkt nedbrutet skick.</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF28" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3600,41 +3600,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128948452</v>
+        <v>125110671</v>
       </c>
       <c r="B29" t="n">
-        <v>92335</v>
+        <v>58353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>366</v>
+        <v>103037</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3642,13 +3643,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579338</v>
+        <v>579247</v>
       </c>
       <c r="R29" t="n">
-        <v>6417742</v>
+        <v>6417660</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3672,12 +3673,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3686,7 +3687,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
